--- a/productos.xlsx
+++ b/productos.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ale\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ale\Documents\GitHub\appPuntoVenta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EF611CD-145E-4F5D-844D-9E8030606A71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EEA8858-A15D-4480-BCDE-06863D54B44F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{77ACDAD0-E555-4A29-BD8E-0943A0472C95}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="26">
   <si>
     <t>agua</t>
   </si>
@@ -97,6 +97,12 @@
   </si>
   <si>
     <t>categoria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alcohol etilico 250 ml  </t>
+  </si>
+  <si>
+    <t>limpieza</t>
   </si>
 </sst>
 </file>
@@ -132,8 +138,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -448,11 +455,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55D29BEC-D929-4E5B-9298-3BBD69B61605}">
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="3" max="3" width="19.140625" customWidth="1"/>
+    <col min="2" max="2" width="18.140625" customWidth="1"/>
+    <col min="3" max="3" width="21.7109375" customWidth="1"/>
     <col min="5" max="5" width="14.85546875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -725,6 +732,23 @@
         <v>7</v>
       </c>
     </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" s="1">
+        <v>7790139000462</v>
+      </c>
+      <c r="C17" t="s">
+        <v>24</v>
+      </c>
+      <c r="D17">
+        <v>2000</v>
+      </c>
+      <c r="E17" t="s">
+        <v>25</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/productos.xlsx
+++ b/productos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ale\Documents\GitHub\appPuntoVenta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EEA8858-A15D-4480-BCDE-06863D54B44F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95BCDBC2-E190-459E-9182-36A3A3EDA3EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{77ACDAD0-E555-4A29-BD8E-0943A0472C95}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="27">
   <si>
     <t>agua</t>
   </si>
@@ -103,6 +103,9 @@
   </si>
   <si>
     <t>limpieza</t>
+  </si>
+  <si>
+    <t>costo</t>
   </si>
 </sst>
 </file>
@@ -455,7 +458,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55D29BEC-D929-4E5B-9298-3BBD69B61605}">
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="18.140625" customWidth="1"/>
@@ -463,7 +466,7 @@
     <col min="5" max="5" width="14.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>19</v>
       </c>
@@ -474,13 +477,16 @@
         <v>21</v>
       </c>
       <c r="D1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E1" t="s">
         <v>22</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -491,13 +497,16 @@
         <v>0</v>
       </c>
       <c r="D2">
+        <v>90</v>
+      </c>
+      <c r="E2">
         <v>100</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -508,13 +517,16 @@
         <v>1</v>
       </c>
       <c r="D3">
+        <v>202</v>
+      </c>
+      <c r="E3">
         <v>232</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -525,13 +537,16 @@
         <v>2</v>
       </c>
       <c r="D4">
+        <v>19000</v>
+      </c>
+      <c r="E4">
         <v>21331</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -542,13 +557,16 @@
         <v>3</v>
       </c>
       <c r="D5">
+        <v>25000</v>
+      </c>
+      <c r="E5">
         <v>28452</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -559,13 +577,16 @@
         <v>4</v>
       </c>
       <c r="D6">
+        <v>35000</v>
+      </c>
+      <c r="E6">
         <v>39067.5</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -576,13 +597,16 @@
         <v>5</v>
       </c>
       <c r="D7">
+        <v>45000</v>
+      </c>
+      <c r="E7">
         <v>49683</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -590,13 +614,16 @@
         <v>6</v>
       </c>
       <c r="D8">
+        <v>55000</v>
+      </c>
+      <c r="E8">
         <v>60298.5</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -607,13 +634,16 @@
         <v>15</v>
       </c>
       <c r="D9">
+        <v>65000</v>
+      </c>
+      <c r="E9">
         <v>70914</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -624,13 +654,16 @@
         <v>8</v>
       </c>
       <c r="D10">
+        <v>76000</v>
+      </c>
+      <c r="E10">
         <v>81529.5</v>
       </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -641,13 +674,16 @@
         <v>9</v>
       </c>
       <c r="D11">
+        <v>85000</v>
+      </c>
+      <c r="E11">
         <v>92145</v>
       </c>
-      <c r="E11" t="s">
+      <c r="F11" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -658,13 +694,16 @@
         <v>10</v>
       </c>
       <c r="D12">
+        <v>95000</v>
+      </c>
+      <c r="E12">
         <v>102760.5</v>
       </c>
-      <c r="E12" t="s">
+      <c r="F12" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
@@ -675,13 +714,16 @@
         <v>11</v>
       </c>
       <c r="D13">
+        <v>95000</v>
+      </c>
+      <c r="E13">
         <v>113376</v>
       </c>
-      <c r="E13" t="s">
+      <c r="F13" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
@@ -692,13 +734,16 @@
         <v>12</v>
       </c>
       <c r="D14">
+        <v>115000</v>
+      </c>
+      <c r="E14">
         <v>123991.5</v>
       </c>
-      <c r="E14" t="s">
+      <c r="F14" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
@@ -709,13 +754,16 @@
         <v>13</v>
       </c>
       <c r="D15">
+        <v>125000</v>
+      </c>
+      <c r="E15">
         <v>134607</v>
       </c>
-      <c r="E15" t="s">
+      <c r="F15" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
@@ -726,13 +774,16 @@
         <v>14</v>
       </c>
       <c r="D16">
+        <v>135000</v>
+      </c>
+      <c r="E16">
         <v>145222.5</v>
       </c>
-      <c r="E16" t="s">
+      <c r="F16" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
@@ -743,9 +794,12 @@
         <v>24</v>
       </c>
       <c r="D17">
+        <v>1400</v>
+      </c>
+      <c r="E17">
         <v>2000</v>
       </c>
-      <c r="E17" t="s">
+      <c r="F17" t="s">
         <v>25</v>
       </c>
     </row>
